--- a/competitor_rd_benchmark.xlsx
+++ b/competitor_rd_benchmark.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="R&amp;D Benchmark" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R&amp;D Benchmark" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,6 +511,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -578,6 +579,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -869,6 +871,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -1086,23 +1089,23 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023 (AR2023)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>not extractable; ~5% of sales (secondary)</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>~5%</t>
-        </is>
+          <t>MSEK 95 expensed product development</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0.023</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Sales MSEK 4,205; most direct CV e-pump comparable; e-products 24% of sales Q1-2024</t>
+          <t>Company income statement (earlier ~5% estimate was wrong); excl. capitalized development (IFRS); gross margin 25.2%</t>
         </is>
       </c>
     </row>
@@ -1162,6 +1165,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
